--- a/artfynd/A 61796-2024 artfynd.xlsx
+++ b/artfynd/A 61796-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376340</v>
       </c>
       <c r="B2" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61796-2024 artfynd.xlsx
+++ b/artfynd/A 61796-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376340</v>
       </c>
       <c r="B2" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61796-2024 artfynd.xlsx
+++ b/artfynd/A 61796-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376340</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61796-2024 artfynd.xlsx
+++ b/artfynd/A 61796-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376340</v>
       </c>
       <c r="B2" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61796-2024 artfynd.xlsx
+++ b/artfynd/A 61796-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376340</v>
       </c>
       <c r="B2" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137376337</v>
       </c>
       <c r="B3" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
